--- a/tests/testdata/excel/ファイル名/R&D_'24 #1 (最終版).xlsx
+++ b/tests/testdata/excel/ファイル名/R&D_'24 #1 (最終版).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DA32A2A-8F48-45CB-AC5D-D36305F6A4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA42C72F-DB39-4EAA-9E30-33BD8CA49FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{63C45206-D342-4333-8477-6FA90F9FCD36}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{87E41204-F9F2-4074-8129-1C65DB1DBC26}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C571BA-EAD7-493F-8C46-FA9F74847585}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6EA9D01-880B-4B31-AE30-DC891436AA83}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/R&D_'24 #1 (最終版).xlsx
+++ b/tests/testdata/excel/ファイル名/R&D_'24 #1 (最終版).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA42C72F-DB39-4EAA-9E30-33BD8CA49FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA0166B4-E9BF-4D14-B6D9-FB89720B0694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{87E41204-F9F2-4074-8129-1C65DB1DBC26}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{1F4AFD52-8CF6-4C46-BD47-098817D92C69}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6EA9D01-880B-4B31-AE30-DC891436AA83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EBECC7-2A6A-45EC-B6DC-B4787C3614D6}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
